--- a/data/ams_weekly_data/Nexlev/ads_report_week26.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week26.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7838,4 +7839,1583 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - SBV- BM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6143</v>
+      </c>
+      <c r="E2" t="n">
+        <v>139</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1715.01</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7540.67</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - BM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>143</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>27.00666666666666</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - BM</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>143</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>27.00666666666666</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - BM</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0GN94YDY2</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>143</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27.00666666666666</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - Exact</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>304</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - Exact</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>304</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - SB - Exact</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0GN94YDY2</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>304</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21</v>
+      </c>
+      <c r="F9" t="n">
+        <v>276.0133333333333</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E10" t="n">
+        <v>21</v>
+      </c>
+      <c r="F10" t="n">
+        <v>276.0133333333333</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - Exact</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0GN94YDY2</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E11" t="n">
+        <v>21</v>
+      </c>
+      <c r="F11" t="n">
+        <v>276.0133333333333</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7503</v>
+      </c>
+      <c r="E12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>893.6900000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7503</v>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>893.6900000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixers - SB - PT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0GN94YDY2</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7503</v>
+      </c>
+      <c r="E14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" t="n">
+        <v>893.6900000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0DM6BB3VT</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14285</v>
+      </c>
+      <c r="E15" t="n">
+        <v>126</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1590.98</v>
+      </c>
+      <c r="G15" t="n">
+        <v>11494.42</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DVSZ2VVJ</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14285</v>
+      </c>
+      <c r="E16" t="n">
+        <v>126</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1590.98</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11494.42</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0FPGDVVCX</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14285</v>
+      </c>
+      <c r="E17" t="n">
+        <v>126</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1590.98</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11494.42</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0D67727VG</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2947</v>
+      </c>
+      <c r="E18" t="n">
+        <v>75</v>
+      </c>
+      <c r="F18" t="n">
+        <v>494.2933333333334</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3991.356666666667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0DCGHKRXX</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2947</v>
+      </c>
+      <c r="E19" t="n">
+        <v>75</v>
+      </c>
+      <c r="F19" t="n">
+        <v>494.2933333333334</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3991.356666666667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2947</v>
+      </c>
+      <c r="E20" t="n">
+        <v>75</v>
+      </c>
+      <c r="F20" t="n">
+        <v>494.2933333333334</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3991.356666666667</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CYSLCRQS-Sofa Vacuum Cleaner -SBV-KT-Phrase</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>15258</v>
+      </c>
+      <c r="E21" t="n">
+        <v>184</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1496.1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>15047</v>
+      </c>
+      <c r="E22" t="n">
+        <v>455</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4254.03</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18723.72</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>16720</v>
+      </c>
+      <c r="E23" t="n">
+        <v>604</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5618.92</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12705.09</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0D67727VG</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>492</v>
+      </c>
+      <c r="E24" t="n">
+        <v>32</v>
+      </c>
+      <c r="F24" t="n">
+        <v>462.015</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>492</v>
+      </c>
+      <c r="E25" t="n">
+        <v>32</v>
+      </c>
+      <c r="F25" t="n">
+        <v>462.015</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3406</v>
+      </c>
+      <c r="E26" t="n">
+        <v>43</v>
+      </c>
+      <c r="F26" t="n">
+        <v>431.69</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5083.9</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7900</v>
+      </c>
+      <c r="E27" t="n">
+        <v>250</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5488.110000000001</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7625.42</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>55377</v>
+      </c>
+      <c r="E28" t="n">
+        <v>468</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7972.07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10591.52</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT02</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>6214</v>
+      </c>
+      <c r="E29" t="n">
+        <v>62</v>
+      </c>
+      <c r="F29" t="n">
+        <v>715.5999999999999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT03</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>28376</v>
+      </c>
+      <c r="E30" t="n">
+        <v>267</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3966.01</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- PT04</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>14338</v>
+      </c>
+      <c r="E31" t="n">
+        <v>132</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1605.44</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12475</v>
+      </c>
+      <c r="E32" t="n">
+        <v>172</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1928.42</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5295.76</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV- Phrase01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>18682</v>
+      </c>
+      <c r="E33" t="n">
+        <v>125</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1719.04</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer- SBV-phrase</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>29165</v>
+      </c>
+      <c r="E34" t="n">
+        <v>123</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1779.89</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7915</v>
+      </c>
+      <c r="E35" t="n">
+        <v>79</v>
+      </c>
+      <c r="F35" t="n">
+        <v>699.5466666666666</v>
+      </c>
+      <c r="G35" t="n">
+        <v>10675.70666666667</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>7915</v>
+      </c>
+      <c r="E36" t="n">
+        <v>79</v>
+      </c>
+      <c r="F36" t="n">
+        <v>699.5466666666666</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10675.70666666667</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>7915</v>
+      </c>
+      <c r="E37" t="n">
+        <v>79</v>
+      </c>
+      <c r="F37" t="n">
+        <v>699.5466666666666</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10675.70666666667</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>14852</v>
+      </c>
+      <c r="E38" t="n">
+        <v>697</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7093.43</v>
+      </c>
+      <c r="G38" t="n">
+        <v>50781.08333333334</v>
+      </c>
+      <c r="H38" t="n">
+        <v>15</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>14852</v>
+      </c>
+      <c r="E39" t="n">
+        <v>697</v>
+      </c>
+      <c r="F39" t="n">
+        <v>7093.43</v>
+      </c>
+      <c r="G39" t="n">
+        <v>50781.08333333334</v>
+      </c>
+      <c r="H39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>14852</v>
+      </c>
+      <c r="E40" t="n">
+        <v>697</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7093.43</v>
+      </c>
+      <c r="G40" t="n">
+        <v>50781.08333333334</v>
+      </c>
+      <c r="H40" t="n">
+        <v>15</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.053333333333333</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>13</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.053333333333333</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamers-Branded</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>13</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.053333333333333</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nexliv-B0DNJS23HS-BM-SBV</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1754</v>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="n">
+        <v>219.06</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>26038</v>
+      </c>
+      <c r="E45" t="n">
+        <v>265</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3219.16</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5761.02</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>6689</v>
+      </c>
+      <c r="E46" t="n">
+        <v>134</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1690.17</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8302.549999999999</v>
+      </c>
+      <c r="H46" t="n">
+        <v>5</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>582</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" t="n">
+        <v>38.92</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>